--- a/artfynd/A 15254-2026 artfynd.xlsx
+++ b/artfynd/A 15254-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132917157</v>
+        <v>132917144</v>
       </c>
       <c r="B2" t="n">
-        <v>79334</v>
+        <v>96410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -713,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496095</v>
+        <v>496093</v>
       </c>
       <c r="R2" t="n">
-        <v>7037472</v>
+        <v>7037420</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +752,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -769,26 +765,6 @@
       <c r="AH2" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,14 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132917149</v>
+        <v>132917145</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -844,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496233</v>
+        <v>496094</v>
       </c>
       <c r="R3" t="n">
-        <v>7037499</v>
+        <v>7037449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,11 +858,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Enstaka bålar på gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -899,7 +870,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -932,14 +903,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132917154</v>
+        <v>132917146</v>
       </c>
       <c r="B4" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -970,10 +941,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496178</v>
+        <v>496154</v>
       </c>
       <c r="R4" t="n">
-        <v>7037397</v>
+        <v>7037446</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,11 +979,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1025,7 +991,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1058,14 +1024,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132917151</v>
+        <v>132917147</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1096,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496233</v>
+        <v>496178</v>
       </c>
       <c r="R5" t="n">
-        <v>7037579</v>
+        <v>7037438</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1184,14 +1150,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132917159</v>
+        <v>132917148</v>
       </c>
       <c r="B6" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1222,10 +1188,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496039</v>
+        <v>496236</v>
       </c>
       <c r="R6" t="n">
-        <v>7037418</v>
+        <v>7037440</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1258,11 +1224,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1310,41 +1271,37 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132917140</v>
+        <v>132917149</v>
       </c>
       <c r="B7" t="n">
-        <v>80468</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1352,10 +1309,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496067</v>
+        <v>496233</v>
       </c>
       <c r="R7" t="n">
-        <v>7037443</v>
+        <v>7037499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1390,6 +1347,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1402,22 +1364,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1435,14 +1397,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132917158</v>
+        <v>132917150</v>
       </c>
       <c r="B8" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1473,10 +1435,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496075</v>
+        <v>496246</v>
       </c>
       <c r="R8" t="n">
-        <v>7037436</v>
+        <v>7037508</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1523,7 +1485,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1556,14 +1518,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132917146</v>
+        <v>132917151</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1594,10 +1556,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496154</v>
+        <v>496233</v>
       </c>
       <c r="R9" t="n">
-        <v>7037446</v>
+        <v>7037579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1630,6 +1592,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1677,14 +1644,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132917156</v>
+        <v>132917152</v>
       </c>
       <c r="B10" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1715,10 +1682,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496112</v>
+        <v>496253</v>
       </c>
       <c r="R10" t="n">
-        <v>7037419</v>
+        <v>7037399</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1783,14 +1750,9 @@
           <t>Picea abies</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1808,14 +1770,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132917147</v>
+        <v>132917153</v>
       </c>
       <c r="B11" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1846,10 +1808,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496178</v>
+        <v>496208</v>
       </c>
       <c r="R11" t="n">
-        <v>7037438</v>
+        <v>7037394</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1884,11 +1846,6 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1901,7 +1858,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1934,14 +1891,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132917150</v>
+        <v>132917154</v>
       </c>
       <c r="B12" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1972,10 +1929,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496246</v>
+        <v>496178</v>
       </c>
       <c r="R12" t="n">
-        <v>7037508</v>
+        <v>7037397</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2010,6 +1967,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2022,7 +1984,7 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -2055,32 +2017,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132917141</v>
+        <v>132917155</v>
       </c>
       <c r="B13" t="n">
-        <v>80439</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2093,10 +2055,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496064</v>
+        <v>496135</v>
       </c>
       <c r="R13" t="n">
-        <v>7037445</v>
+        <v>7037381</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2133,7 +2095,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Enstaka bålar på en smal sälg.</t>
+          <t>På grenar av en stående död gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2153,22 +2115,22 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2186,14 +2148,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132917153</v>
+        <v>132917156</v>
       </c>
       <c r="B14" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2224,10 +2186,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496208</v>
+        <v>496112</v>
       </c>
       <c r="R14" t="n">
-        <v>7037394</v>
+        <v>7037419</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2262,6 +2224,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2287,9 +2254,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2307,14 +2279,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132917145</v>
+        <v>132917157</v>
       </c>
       <c r="B15" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2345,10 +2317,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496094</v>
+        <v>496095</v>
       </c>
       <c r="R15" t="n">
-        <v>7037449</v>
+        <v>7037472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2383,6 +2355,11 @@
           <t>2026-04-23</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2408,9 +2385,14 @@
           <t>Picea abies</t>
         </is>
       </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2428,14 +2410,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132917152</v>
+        <v>132917158</v>
       </c>
       <c r="B16" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2466,10 +2448,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496253</v>
+        <v>496075</v>
       </c>
       <c r="R16" t="n">
-        <v>7037399</v>
+        <v>7037436</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2502,11 +2484,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-04-23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2554,14 +2531,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132917148</v>
+        <v>132917159</v>
       </c>
       <c r="B17" t="n">
-        <v>79334</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2592,10 +2569,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496236</v>
+        <v>496039</v>
       </c>
       <c r="R17" t="n">
-        <v>7037440</v>
+        <v>7037418</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2628,6 +2605,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2675,10 +2657,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132917135</v>
+        <v>132917141</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>80488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2686,31 +2668,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2718,10 +2695,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496227</v>
+        <v>496064</v>
       </c>
       <c r="R18" t="n">
-        <v>7037521</v>
+        <v>7037445</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2758,7 +2735,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, högt upp på en tall.</t>
+          <t>Enstaka bålar på en smal sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2767,32 +2744,33 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2810,40 +2788,39 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132917134</v>
+        <v>132917140</v>
       </c>
       <c r="B19" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2853,10 +2830,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496168</v>
+        <v>496067</v>
       </c>
       <c r="R19" t="n">
-        <v>7037432</v>
+        <v>7037443</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2891,38 +2868,34 @@
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2940,7 +2913,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132917138</v>
+        <v>132917134</v>
       </c>
       <c r="B20" t="n">
         <v>57975</v>
@@ -2973,7 +2946,7 @@
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2983,10 +2956,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496133</v>
+        <v>496168</v>
       </c>
       <c r="R20" t="n">
-        <v>7037449</v>
+        <v>7037432</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3023,21 +2996,21 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Påbörjat nytt bohål? 40 mm i diameter på 1,7 m höjd i döende gran.</t>
+          <t>Ringhack, äldre, enstaka på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3070,7 +3043,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132917139</v>
+        <v>132917135</v>
       </c>
       <c r="B21" t="n">
         <v>57975</v>
@@ -3113,10 +3086,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496125</v>
+        <v>496227</v>
       </c>
       <c r="R21" t="n">
-        <v>7037457</v>
+        <v>7037521</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3153,7 +3126,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på stambasen av en gran.</t>
+          <t>Ringhack, äldre, högt upp på en tall.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3167,17 +3140,17 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -3187,7 +3160,7 @@
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -3338,6 +3311,609 @@
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132917138</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nordväst om Gulåsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>496133</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7037449</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Påbörjat nytt bohål? 40 mm i diameter på 1,7 m höjd i döende gran.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132917139</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Nordväst om Gulåsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>496125</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7037457</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på stambasen av en gran.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132917160</v>
+      </c>
+      <c r="B25" t="n">
+        <v>108205</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220083</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Brudborste</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Cirsium heterophyllum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>gulnande löv/blad</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Nordväst om Gulåsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>496102</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7037469</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132917142</v>
+      </c>
+      <c r="B26" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Nordväst om Gulåsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>496209</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7037420</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132917143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>111153</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220240</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Linnea</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Linnaea borealis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Nordväst om Gulåsbodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>496082</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7037429</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Häggenås</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med inslag av björk, sälg och tall.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 15254-2026 artfynd.xlsx
+++ b/artfynd/A 15254-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917144</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917145</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917146</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1147,6 +1167,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917147</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1268,6 +1293,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917148</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1394,6 +1424,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917149</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1515,6 +1550,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917150</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1641,6 +1681,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917151</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1767,6 +1812,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917152</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1888,6 +1938,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917153</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2014,6 +2069,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917154</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2145,6 +2205,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917155</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2276,6 +2341,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917156</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2407,6 +2477,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917157</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2528,6 +2603,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917158</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2654,6 +2734,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917159</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2785,6 +2870,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917141</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2910,6 +3000,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917140</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3040,6 +3135,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917134</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3175,6 +3275,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917135</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3310,6 +3415,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917136</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3440,6 +3550,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917138</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3575,6 +3690,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917139</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3686,6 +3806,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917160</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3797,6 +3922,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917142</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3913,8 +4043,41 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132917143</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>